--- a/output/pdf_financials_xlsx/NEW.H.xlsx
+++ b/output/pdf_financials_xlsx/NEW.H.xlsx
@@ -2802,19 +2802,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="93">
@@ -4314,7 +4314,11 @@
           <t>Share-based payment reserve (Note 3)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4616,7 +4620,11 @@
           <t>Share-based payment reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4830,7 +4838,11 @@
           <t>Share-based payment reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NEW.H.xlsx
+++ b/output/pdf_financials_xlsx/NEW.H.xlsx
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009959999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1121,7 +1121,7 @@
         <v>-0.162242</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.114337</v>
+        <v>-0.115333</v>
       </c>
     </row>
     <row r="28">
@@ -1171,7 +1171,7 @@
         <v>-0.162242</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.114337</v>
+        <v>-0.115333</v>
       </c>
     </row>
     <row r="30">
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.25021</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.397624</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.185191</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.107007</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.041702</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.292032</v>
       </c>
     </row>
     <row r="35">
@@ -1337,22 +1337,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.25021</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.397624</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.185191</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.107007</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.041702</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.292032</v>
       </c>
     </row>
     <row r="37">
@@ -1637,16 +1637,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.25021</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.404916</v>
+        <v>0.007292</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.191091</v>
+        <v>0.0059</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.111357</v>
+        <v>0.00435</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">

--- a/output/pdf_financials_xlsx/NEW.H.xlsx
+++ b/output/pdf_financials_xlsx/NEW.H.xlsx
@@ -5226,7 +5226,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
